--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Auto ETF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Auto ETF.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="73">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty Auto ETF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -115,19 +115,31 @@
     <t>Auto Components</t>
   </si>
   <si>
+    <t>Ashok Leyland Ltd.</t>
+  </si>
+  <si>
+    <t>INE208A01029</t>
+  </si>
+  <si>
+    <t>Agricultural, Commercial &amp; Construction Vehicles</t>
+  </si>
+  <si>
     <t>Bharat Forge Ltd.</t>
   </si>
   <si>
     <t>INE465A01025</t>
   </si>
   <si>
-    <t>Ashok Leyland Ltd.</t>
-  </si>
-  <si>
-    <t>INE208A01029</t>
-  </si>
-  <si>
-    <t>Agricultural, Commercial &amp; Construction Vehicles</t>
+    <t>Tube Investments of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE974X01010</t>
+  </si>
+  <si>
+    <t>MRF Ltd.</t>
+  </si>
+  <si>
+    <t>INE883A01011</t>
   </si>
   <si>
     <t>Bosch Ltd.</t>
@@ -136,12 +148,6 @@
     <t>INE323A01026</t>
   </si>
   <si>
-    <t>MRF Ltd.</t>
-  </si>
-  <si>
-    <t>INE883A01011</t>
-  </si>
-  <si>
     <t>Balkrishna Industries Ltd.</t>
   </si>
   <si>
@@ -154,12 +160,6 @@
     <t>INE302A01020</t>
   </si>
   <si>
-    <t>Apollo Tyres Ltd.</t>
-  </si>
-  <si>
-    <t>INE438A01022</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>TREPS</t>
   </si>
   <si>
+    <t>^</t>
+  </si>
+  <si>
     <t>Net Current Assets</t>
   </si>
   <si>
@@ -211,13 +214,16 @@
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
+    <t>^ Value Less than 0.01% of NAV in absolute terms.</t>
+  </si>
+  <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
   </si>
   <si>
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -227,9 +233,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - Nifty Auto TRI</t>
   </si>
 </sst>
 </file>
@@ -600,13 +603,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>76</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -624,7 +627,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="12839700"/>
+          <a:off x="666750" y="13030200"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -639,13 +642,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -663,7 +666,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="15697200"/>
+          <a:off x="666750" y="15887700"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1097,10 +1100,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>11943.210000000001</v>
+        <v>12454.48</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9999368965505</v>
+        <v>0.9995153803708999</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1134,10 +1137,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>11943.210000000001</v>
+        <v>12454.48</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9999368965505</v>
+        <v>0.9995153803708999</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1160,13 +1163,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>99131</v>
+        <v>100030</v>
       </c>
       <c r="G8" s="15">
-        <v>2963.87</v>
+        <v>2977.69</v>
       </c>
       <c r="H8" s="16">
-        <v>0.2481479409289</v>
+        <v>0.2389699893515</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1189,13 +1192,13 @@
         <v>17</v>
       </c>
       <c r="F9" s="14">
-        <v>14734</v>
+        <v>14815</v>
       </c>
       <c r="G9" s="15">
-        <v>1813.85</v>
+        <v>1825.06</v>
       </c>
       <c r="H9" s="16">
-        <v>0.1518633214864</v>
+        <v>0.1464674189609</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1218,13 +1221,13 @@
         <v>17</v>
       </c>
       <c r="F10" s="14">
-        <v>234708</v>
+        <v>235563</v>
       </c>
       <c r="G10" s="15">
-        <v>1680.74</v>
+        <v>1694.88</v>
       </c>
       <c r="H10" s="16">
-        <v>0.1407187799184</v>
+        <v>0.1360200207382</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1247,13 +1250,13 @@
         <v>17</v>
       </c>
       <c r="F11" s="14">
-        <v>12422</v>
+        <v>12518</v>
       </c>
       <c r="G11" s="15">
-        <v>1099.07</v>
+        <v>1077.42</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0920188663594</v>
+        <v>0.0864667060463</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1276,13 +1279,13 @@
         <v>17</v>
       </c>
       <c r="F12" s="14">
-        <v>15406</v>
+        <v>15518</v>
       </c>
       <c r="G12" s="15">
-        <v>800.23</v>
+        <v>827.65</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0669986965587</v>
+        <v>0.06642179397</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1305,13 +1308,13 @@
         <v>17</v>
       </c>
       <c r="F13" s="14">
-        <v>26259</v>
+        <v>26521</v>
       </c>
       <c r="G13" s="15">
-        <v>645.42</v>
+        <v>737.50</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0540373376815</v>
+        <v>0.0591869426121</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1334,13 +1337,13 @@
         <v>17</v>
       </c>
       <c r="F14" s="14">
-        <v>14514</v>
+        <v>14659</v>
       </c>
       <c r="G14" s="15">
-        <v>629.78</v>
+        <v>631.7</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0527278896301</v>
+        <v>0.0506961242685</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1363,13 +1366,13 @@
         <v>32</v>
       </c>
       <c r="F15" s="14">
-        <v>330050</v>
+        <v>332845</v>
       </c>
       <c r="G15" s="15">
-        <v>466.23</v>
+        <v>509.65</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0390347803713</v>
+        <v>0.0409011868505</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1389,16 +1392,16 @@
         <v>13</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F16" s="14">
-        <v>29289</v>
+        <v>161451</v>
       </c>
       <c r="G16" s="15">
-        <v>358.51</v>
+        <v>381.07</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0300159987794</v>
+        <v>0.0305821941982</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1409,25 +1412,25 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F17" s="14">
-        <v>160259</v>
+        <v>30130</v>
       </c>
       <c r="G17" s="15">
-        <v>347.49</v>
+        <v>373.88</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0290933569938</v>
+        <v>0.0300051716662</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1450,13 +1453,13 @@
         <v>32</v>
       </c>
       <c r="F18" s="14">
-        <v>969</v>
+        <v>12144</v>
       </c>
       <c r="G18" s="15">
-        <v>278.39</v>
+        <v>371.86</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0233080078664</v>
+        <v>0.0298430596335</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1479,13 +1482,13 @@
         <v>32</v>
       </c>
       <c r="F19" s="14">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G19" s="15">
-        <v>256.81</v>
+        <v>316.61</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0215012374732</v>
+        <v>0.0254090547802</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1508,13 +1511,13 @@
         <v>32</v>
       </c>
       <c r="F20" s="14">
-        <v>8986</v>
+        <v>978</v>
       </c>
       <c r="G20" s="15">
-        <v>249.02</v>
+        <v>307.24</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0208490251765</v>
+        <v>0.0246570796585</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1537,13 +1540,13 @@
         <v>32</v>
       </c>
       <c r="F21" s="14">
-        <v>50949</v>
+        <v>9047</v>
       </c>
       <c r="G21" s="15">
-        <v>190.80</v>
+        <v>223.66</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0159745964327</v>
+        <v>0.017949493674</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1566,13 +1569,13 @@
         <v>32</v>
       </c>
       <c r="F22" s="14">
-        <v>37274</v>
+        <v>51340</v>
       </c>
       <c r="G22" s="15">
-        <v>163</v>
+        <v>198.61</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0136470608938</v>
+        <v>0.0159391439623</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -2087,10 +2090,10 @@
         <v>13</v>
       </c>
       <c r="G50" s="9">
-        <v>3.16</v>
-      </c>
-      <c r="H50" s="10">
-        <v>0.0002645687878</v>
+        <v>0.45</v>
+      </c>
+      <c r="H50" s="16" t="s">
+        <v>62</v>
       </c>
       <c r="I50" s="9" t="s">
         <v>13</v>
@@ -2109,7 +2112,7 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C52" s="18" t="s">
         <v>13</v>
@@ -2124,10 +2127,10 @@
         <v>13</v>
       </c>
       <c r="G52" s="18">
-        <v>-2.406294699996579</v>
+        <v>5.588611899998796</v>
       </c>
       <c r="H52" s="19">
-        <v>-0.00020146533925993198</v>
+        <v>0.00044850556177184945</v>
       </c>
       <c r="I52" s="18" t="s">
         <v>13</v>
@@ -2138,7 +2141,7 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C53" s="18" t="s">
         <v>13</v>
@@ -2153,10 +2156,10 @@
         <v>13</v>
       </c>
       <c r="G53" s="18">
-        <v>11943.9637053</v>
+        <v>12460.5186119</v>
       </c>
       <c r="H53" s="19">
-        <v>0.9999999999990401</v>
+        <v>0.9999999999992718</v>
       </c>
       <c r="I53" s="18" t="s">
         <v>13</v>
@@ -2167,7 +2170,7 @@
     </row>
     <row r="56" spans="2:9" ht="15" customHeight="1">
       <c r="B56" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C56" s="21"/>
       <c r="D56" s="21"/>
@@ -2179,7 +2182,7 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C57" s="21"/>
       <c r="D57" s="21"/>
@@ -2188,9 +2191,9 @@
       <c r="G57" s="21"/>
       <c r="H57" s="21"/>
     </row>
-    <row r="58" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B58" s="22" t="s">
-        <v>66</v>
+    <row r="58" spans="2:8" ht="15" customHeight="1">
+      <c r="B58" s="13" t="s">
+        <v>67</v>
       </c>
       <c r="C58" s="21"/>
       <c r="D58" s="21"/>
@@ -2201,7 +2204,7 @@
     </row>
     <row r="59" spans="2:8" ht="27.6" customHeight="1">
       <c r="B59" s="22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C59" s="21"/>
       <c r="D59" s="21"/>
@@ -2212,7 +2215,7 @@
     </row>
     <row r="60" spans="2:8" ht="27.6" customHeight="1">
       <c r="B60" s="22" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
@@ -2221,26 +2224,33 @@
       <c r="G60" s="21"/>
       <c r="H60" s="21"/>
     </row>
-    <row r="63" ht="15">
-      <c r="B63" s="21" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="78" ht="15">
-      <c r="B78" s="21" t="s">
+    <row r="61" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B61" s="22" t="s">
         <v>70</v>
+      </c>
+      <c r="C61" s="21"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="21"/>
+      <c r="G61" s="21"/>
+      <c r="H61" s="21"/>
+    </row>
+    <row r="64" ht="15">
+      <c r="B64" s="21" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="79" ht="15">
       <c r="B79" s="21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="B58:H58"/>
     <mergeCell ref="B59:H59"/>
     <mergeCell ref="B60:H60"/>
+    <mergeCell ref="B61:H61"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
